--- a/信息检索与数据挖掘作业/第一次论文研读/数据备份.xlsx
+++ b/信息检索与数据挖掘作业/第一次论文研读/数据备份.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29870" windowHeight="13360"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>会议名称</t>
+  </si>
+  <si>
+    <t>论文标题</t>
+  </si>
+  <si>
+    <t>论文链接</t>
+  </si>
+  <si>
+    <t>豆包对话链接</t>
+  </si>
+  <si>
+    <t>阅读笔记链接</t>
+  </si>
+  <si>
+    <t>1.问题陈述</t>
+  </si>
+  <si>
+    <t>2.方法概述</t>
+  </si>
+  <si>
+    <t>3.实验</t>
+  </si>
+  <si>
+    <t>4.思考</t>
+  </si>
+  <si>
+    <t>5.其它（选填）</t>
+  </si>
   <si>
     <t>宋浩宇</t>
   </si>
@@ -68,7 +101,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,22 +110,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="0"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -241,12 +281,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4874CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -561,55 +607,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
@@ -624,87 +667,96 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,23 +1070,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="9.81818181818182" customWidth="1"/>
+    <col min="2" max="2" width="10.3636363636364" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11.9090909090909" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="11.8181818181818" customWidth="1"/>
+    <col min="9" max="9" width="13.8181818181818" customWidth="1"/>
+    <col min="10" max="10" width="11.8181818181818" customWidth="1"/>
+    <col min="11" max="11" width="12.3636363636364" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="362.5" spans="1:10">
+    <row r="1" ht="33" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1049,13 +1112,49 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="280.5" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" display="https://arxiv.org/abs/2503.03733" tooltip="https://arxiv.org/abs/2503.03733"/>
-    <hyperlink ref="D1" r:id="rId2" display="https://www.doubao.com/thread/w02b19d6e37dde0ee" tooltip="https://www.doubao.com/thread/w02b19d6e37dde0ee"/>
-    <hyperlink ref="E1" r:id="rId3" display="https://jcn5ed29kssw.feishu.cn/wiki/I11Dwc6HXivE5FkKd7WcqL4Znov?from=from_copylink" tooltip="https://jcn5ed29kssw.feishu.cn/wiki/I11Dwc6HXivE5FkKd7WcqL4Znov?from=from_copylink"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://arxiv.org/abs/2503.03733" tooltip="https://arxiv.org/abs/2503.03733"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://www.doubao.com/thread/w02b19d6e37dde0ee" tooltip="https://www.doubao.com/thread/w02b19d6e37dde0ee"/>
+    <hyperlink ref="F2" r:id="rId3" display="https://jcn5ed29kssw.feishu.cn/wiki/I11Dwc6HXivE5FkKd7WcqL4Znov?from=from_copylink" tooltip="https://jcn5ed29kssw.feishu.cn/wiki/I11Dwc6HXivE5FkKd7WcqL4Znov?from=from_copylink"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
